--- a/artfynd/A 31015-2022 artfynd.xlsx
+++ b/artfynd/A 31015-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,435 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130651842</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58532</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NV Lidtjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>331931</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6555555</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En flock, förbiflygande</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130651726</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58224</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NV Lidtjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>332075</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6555344</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130651808</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58011</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NV Lidtjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>331998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6555395</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130651688</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58532</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NV Lidtjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>332014</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6555360</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2025</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 31015-2022 artfynd.xlsx
+++ b/artfynd/A 31015-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130651842</v>
       </c>
       <c r="B3" t="n">
-        <v>58532</v>
+        <v>58534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>130651726</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130651808</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130651688</v>
       </c>
       <c r="B6" t="n">
-        <v>58532</v>
+        <v>58534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31015-2022 artfynd.xlsx
+++ b/artfynd/A 31015-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130651842</v>
       </c>
       <c r="B3" t="n">
-        <v>58534</v>
+        <v>58542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>130651726</v>
       </c>
       <c r="B4" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130651808</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130651688</v>
       </c>
       <c r="B6" t="n">
-        <v>58534</v>
+        <v>58542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31015-2022 artfynd.xlsx
+++ b/artfynd/A 31015-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130651842</v>
       </c>
       <c r="B3" t="n">
-        <v>58542</v>
+        <v>58543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>130651726</v>
       </c>
       <c r="B4" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130651808</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130651688</v>
       </c>
       <c r="B6" t="n">
-        <v>58542</v>
+        <v>58543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31015-2022 artfynd.xlsx
+++ b/artfynd/A 31015-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130651842</v>
       </c>
       <c r="B3" t="n">
-        <v>58543</v>
+        <v>58544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>130651726</v>
       </c>
       <c r="B4" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130651808</v>
       </c>
       <c r="B5" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130651688</v>
       </c>
       <c r="B6" t="n">
-        <v>58543</v>
+        <v>58544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31015-2022 artfynd.xlsx
+++ b/artfynd/A 31015-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120447408</v>
+        <v>130651726</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,29 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SO om Askesjö, Dls</t>
+          <t>NV Lidtjärnet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332032</v>
+        <v>332075</v>
       </c>
       <c r="R2" t="n">
-        <v>6555370</v>
+        <v>6555344</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +765,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -784,44 +775,44 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Fågelinventering Klinthögen 2024</t>
+          <t>Fågelinventering Klinthögen 2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130651842</v>
+        <v>130651808</v>
       </c>
       <c r="B3" t="n">
-        <v>58564</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>331931</v>
+        <v>331998</v>
       </c>
       <c r="R3" t="n">
-        <v>6555555</v>
+        <v>6555395</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En flock, förbiflygande</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130651726</v>
+        <v>120447408</v>
       </c>
       <c r="B4" t="n">
-        <v>58256</v>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,16 +898,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,25 +915,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NV Lidtjärnet, Dls</t>
+          <t>SO om Askesjö, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332075</v>
+        <v>332032</v>
       </c>
       <c r="R4" t="n">
-        <v>6555344</v>
+        <v>6555370</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,44 +991,44 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Fågelinventering Klinthögen 2025</t>
+          <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130651808</v>
+        <v>130651688</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>58636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>331998</v>
+        <v>332014</v>
       </c>
       <c r="R5" t="n">
-        <v>6555395</v>
+        <v>6555360</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130651688</v>
+        <v>130651842</v>
       </c>
       <c r="B6" t="n">
-        <v>58564</v>
+        <v>58636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>332014</v>
+        <v>331931</v>
       </c>
       <c r="R6" t="n">
-        <v>6555360</v>
+        <v>6555555</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,12 +1173,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En flock, förbiflygande</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 31015-2022 artfynd.xlsx
+++ b/artfynd/A 31015-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Fågelinventering Klinthögen 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130651726</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Fågelinventering Klinthögen 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130651808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
           <t>Fågelinventering Klinthögen 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130651688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,8 +1236,20 @@
           <t>Fågelinventering Klinthögen 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130651842</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>